--- a/test-case-document.xlsx
+++ b/test-case-document.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\308345\Documents\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798B7862-655B-43FE-93AA-CA21F3A0431D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D334C5D-5896-41B7-8967-CD5E175F9A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA7E9C1-195C-467C-A706-79A11DB80961}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -232,6 +232,37 @@
   </si>
   <si>
     <t>User is able to type "standard_user" in username and "secret_sauce" in password</t>
+  </si>
+  <si>
+    <t>TC_SwagLabs_06</t>
+  </si>
+  <si>
+    <t>TS_SwagLabs_06</t>
+  </si>
+  <si>
+    <t>To validate the add-to-cart functionality</t>
+  </si>
+  <si>
+    <t>1.Open &lt;browser&gt;
+2.Enter the &lt;URL&gt;
+3.Enter &lt;username&gt;
+4.Enter &lt;password&gt;
+5.Click on login button
+6.select a product and click add to cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browser :  Edge
+URL : //https://saucedemo.com
+Username : stanadard_user
+Password : secret_sauce
+Product Name : sauce labs backpack
+</t>
+  </si>
+  <si>
+    <t>User to able to add an product to the cart and button text changed to remove</t>
+  </si>
+  <si>
+    <t>User is able to add "Sauce Labs Backpack" into cart and button text changed from "add to cart" to remove</t>
   </si>
 </sst>
 </file>
@@ -299,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -311,9 +342,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -653,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6ACE9B-EE94-4CFF-BC74-AFEB3CBF266C}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" style="1" customWidth="1"/>
@@ -731,10 +759,10 @@
       <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -760,10 +788,10 @@
       <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -789,10 +817,10 @@
       <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -818,10 +846,10 @@
       <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -847,10 +875,10 @@
       <c r="G6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -876,10 +904,10 @@
       <c r="G7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -905,10 +933,10 @@
       <c r="G8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -934,10 +962,39 @@
       <c r="G9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
